--- a/NWspecies050122.xlsx
+++ b/NWspecies050122.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4fad9919cbe5b/Neighbourwoods/NWAnalytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{331C3DD1-AED7-457F-8D54-33BE38FF1221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:40009_{331C3DD1-AED7-457F-8D54-33BE38FF1221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1081FCDB-AF0B-4CE6-B398-0A6196BCD71F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView minimized="1" xWindow="7560" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="species" sheetId="1" r:id="rId1"/>
     <sheet name="all data" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -5192,7 +5203,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5754,9 +5765,9 @@
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="42"/>
-    <cellStyle name="Normal 2 2" xfId="43"/>
-    <cellStyle name="Normal 3 2" xfId="44"/>
+    <cellStyle name="Normal 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 2 2" xfId="43" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal 3 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -6072,16 +6083,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" customWidth="1"/>
     <col min="15" max="15" width="15.85546875" customWidth="1"/>
     <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -20332,7 +20345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:BG300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
